--- a/Use-Case_Description--Process_an_Uploaded_Audio_File.xlsx
+++ b/Use-Case_Description--Process_an_Uploaded_Audio_File.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0985F1-59DC-4EBC-A12F-7BB3C8619075}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24202778-2B96-4DFC-9B37-407143DE17DA}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19360" yWindow="1490" windowWidth="18930" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
+    <workbookView xWindow="19340" yWindow="1490" windowWidth="18930" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>1. The TBD signals desire to select an uploaded audio file to be processed.
-2. The system provides to the TBD the set of all unprocessed uploaded audio files.
+2. The system provides to the TBD the set of all unprocessed uploaded audio files for which the TBD has permission to process.
 3. The Uploader / Submitter uploads the audio file.
 4. The Uploader / Submitter requests that the system process the uploaded audio file.
 5. The system processes the uploaded audio file.
@@ -837,7 +837,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="116" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>25</v>
       </c>
